--- a/artfynd/A 22677-2024 artfynd.xlsx
+++ b/artfynd/A 22677-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118505021</v>
+        <v>118502499</v>
       </c>
       <c r="B4" t="n">
-        <v>90504</v>
+        <v>56502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,25 +937,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -965,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>677169</v>
+        <v>677156</v>
       </c>
       <c r="R4" t="n">
-        <v>7085612</v>
+        <v>7085436</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118515803</v>
+        <v>118505495</v>
       </c>
       <c r="B5" t="n">
-        <v>90504</v>
+        <v>79565</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,40 +1053,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SCA, Ång</t>
+          <t>Lillmyran (Lillmyran), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>677056</v>
+        <v>677182</v>
       </c>
       <c r="R5" t="n">
-        <v>7085748</v>
+        <v>7085673</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,18 +1110,27 @@
           <t>2024-07-17</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-17</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1143,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118505495</v>
+        <v>118505021</v>
       </c>
       <c r="B6" t="n">
-        <v>79565</v>
+        <v>90504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1165,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677182</v>
+        <v>677169</v>
       </c>
       <c r="R6" t="n">
-        <v>7085673</v>
+        <v>7085612</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1218,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118502499</v>
+        <v>118514384</v>
       </c>
       <c r="B7" t="n">
-        <v>56502</v>
+        <v>90451</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,41 +1273,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>112</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillmyran (Lillmyran), Ång</t>
+          <t>SCA, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>677156</v>
+        <v>677104</v>
       </c>
       <c r="R7" t="n">
-        <v>7085436</v>
+        <v>7085770</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,27 +1341,18 @@
           <t>2024-07-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-17</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1367,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118514384</v>
+        <v>118504168</v>
       </c>
       <c r="B8" t="n">
-        <v>90451</v>
+        <v>90694</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,48 +1383,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>SCA, Ång</t>
+          <t>Lillmyran (Lillmyran), Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>677104</v>
+        <v>677154</v>
       </c>
       <c r="R8" t="n">
-        <v>7085770</v>
+        <v>7085619</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,18 +1444,27 @@
           <t>2024-07-17</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-17</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1477,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118504168</v>
+        <v>118713061</v>
       </c>
       <c r="B9" t="n">
-        <v>90694</v>
+        <v>56502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,41 +1495,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillmyran (Lillmyran), Ång</t>
+          <t>A 22677-2024, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>677154</v>
+        <v>676939</v>
       </c>
       <c r="R9" t="n">
-        <v>7085619</v>
+        <v>7085624</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,19 +1556,9 @@
           <t>2024-07-17</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,22 +1573,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118713060</v>
+        <v>118713054</v>
       </c>
       <c r="B10" t="n">
-        <v>97763</v>
+        <v>79565</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,25 +1597,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1629,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>676881</v>
+        <v>677120</v>
       </c>
       <c r="R10" t="n">
-        <v>7085506</v>
+        <v>7085431</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118713050</v>
+        <v>118713066</v>
       </c>
       <c r="B11" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1707,21 +1703,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1731,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>677135</v>
+        <v>677082</v>
       </c>
       <c r="R11" t="n">
-        <v>7085535</v>
+        <v>7085390</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1769,13 +1765,17 @@
           <t>2024-07-17</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt på tallstam</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2003,10 +2003,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118713054</v>
+        <v>118713063</v>
       </c>
       <c r="B14" t="n">
-        <v>79565</v>
+        <v>57181</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,21 +2019,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>677120</v>
+        <v>677034</v>
       </c>
       <c r="R14" t="n">
-        <v>7085431</v>
+        <v>7085686</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,6 +2079,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Fågelbo på stam av rovfågel</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2105,10 +2110,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118713062</v>
+        <v>118713060</v>
       </c>
       <c r="B15" t="n">
-        <v>78484</v>
+        <v>97763</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2117,25 +2122,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2145,10 +2150,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>676975</v>
+        <v>676881</v>
       </c>
       <c r="R15" t="n">
-        <v>7085592</v>
+        <v>7085506</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2207,10 +2212,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118713063</v>
+        <v>118713048</v>
       </c>
       <c r="B16" t="n">
-        <v>57181</v>
+        <v>90522</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2223,21 +2228,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100001</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2247,10 +2252,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>677034</v>
+        <v>677129</v>
       </c>
       <c r="R16" t="n">
-        <v>7085686</v>
+        <v>7085711</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2283,11 +2288,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-07-17</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fågelbo på stam av rovfågel</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2314,10 +2314,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118713061</v>
+        <v>118713062</v>
       </c>
       <c r="B17" t="n">
-        <v>56502</v>
+        <v>78484</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2326,25 +2326,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>676939</v>
+        <v>676975</v>
       </c>
       <c r="R17" t="n">
-        <v>7085624</v>
+        <v>7085592</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118713048</v>
+        <v>118713050</v>
       </c>
       <c r="B18" t="n">
-        <v>90522</v>
+        <v>79565</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>677129</v>
+        <v>677135</v>
       </c>
       <c r="R18" t="n">
-        <v>7085711</v>
+        <v>7085535</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2500,6 +2500,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2518,10 +2519,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118713066</v>
+        <v>118515803</v>
       </c>
       <c r="B19" t="n">
-        <v>78484</v>
+        <v>90469</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2530,41 +2531,44 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 22677-2024, Ång</t>
+          <t>SCA, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>677082</v>
+        <v>677056</v>
       </c>
       <c r="R19" t="n">
-        <v>7085390</v>
+        <v>7085748</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2596,32 +2600,134 @@
           <t>2024-07-17</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt på tallstam</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>118883686</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57181</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Accipiter gentilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SCA, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>676942</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7085721</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22677-2024 artfynd.xlsx
+++ b/artfynd/A 22677-2024 artfynd.xlsx
@@ -1483,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118713061</v>
+        <v>118713055</v>
       </c>
       <c r="B9" t="n">
-        <v>56502</v>
+        <v>78484</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,25 +1495,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>676939</v>
+        <v>677125</v>
       </c>
       <c r="R9" t="n">
-        <v>7085624</v>
+        <v>7085428</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,6 +1559,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt på tallstam</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118713054</v>
+        <v>118713048</v>
       </c>
       <c r="B10" t="n">
-        <v>79565</v>
+        <v>90522</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,21 +1606,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1625,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>677120</v>
+        <v>677129</v>
       </c>
       <c r="R10" t="n">
-        <v>7085431</v>
+        <v>7085711</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1794,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118713055</v>
+        <v>118713060</v>
       </c>
       <c r="B12" t="n">
-        <v>78484</v>
+        <v>97763</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,25 +1811,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1834,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>677125</v>
+        <v>676881</v>
       </c>
       <c r="R12" t="n">
-        <v>7085428</v>
+        <v>7085506</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,11 +1875,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt på tallstam</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2003,10 +2003,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118713063</v>
+        <v>118713061</v>
       </c>
       <c r="B14" t="n">
-        <v>57181</v>
+        <v>56502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2015,25 +2015,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100001</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>677034</v>
+        <v>676939</v>
       </c>
       <c r="R14" t="n">
-        <v>7085686</v>
+        <v>7085624</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,11 +2079,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Fågelbo på stam av rovfågel</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,10 +2105,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118713060</v>
+        <v>118713063</v>
       </c>
       <c r="B15" t="n">
-        <v>97763</v>
+        <v>57181</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2122,25 +2117,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>100001</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2150,10 +2145,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>676881</v>
+        <v>677034</v>
       </c>
       <c r="R15" t="n">
-        <v>7085506</v>
+        <v>7085686</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,6 +2181,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Fågelbo på stam av rovfågel</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,10 +2212,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118713048</v>
+        <v>118713054</v>
       </c>
       <c r="B16" t="n">
-        <v>90522</v>
+        <v>79565</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2228,21 +2228,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>677129</v>
+        <v>677120</v>
       </c>
       <c r="R16" t="n">
-        <v>7085711</v>
+        <v>7085431</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 22677-2024 artfynd.xlsx
+++ b/artfynd/A 22677-2024 artfynd.xlsx
@@ -1040,7 +1040,7 @@
         <v>118505495</v>
       </c>
       <c r="B5" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>118505021</v>
       </c>
       <c r="B6" t="n">
-        <v>90504</v>
+        <v>90511</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>118514384</v>
       </c>
       <c r="B7" t="n">
-        <v>90451</v>
+        <v>90458</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>118504168</v>
       </c>
       <c r="B8" t="n">
-        <v>90694</v>
+        <v>90701</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1483,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118713055</v>
+        <v>118713066</v>
       </c>
       <c r="B9" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>677125</v>
+        <v>677082</v>
       </c>
       <c r="R9" t="n">
-        <v>7085428</v>
+        <v>7085390</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118713048</v>
+        <v>118713061</v>
       </c>
       <c r="B10" t="n">
-        <v>90522</v>
+        <v>56502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,25 +1602,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>677129</v>
+        <v>676939</v>
       </c>
       <c r="R10" t="n">
-        <v>7085711</v>
+        <v>7085624</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118713066</v>
+        <v>118713050</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
+        <v>79572</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,21 +1708,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>677082</v>
+        <v>677135</v>
       </c>
       <c r="R11" t="n">
-        <v>7085390</v>
+        <v>7085535</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,17 +1770,13 @@
           <t>2024-07-17</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt på tallstam</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1799,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118713060</v>
+        <v>118713055</v>
       </c>
       <c r="B12" t="n">
-        <v>97763</v>
+        <v>78491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1839,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>676881</v>
+        <v>677125</v>
       </c>
       <c r="R12" t="n">
-        <v>7085506</v>
+        <v>7085428</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,6 +1871,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt på tallstam</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118713064</v>
+        <v>118713060</v>
       </c>
       <c r="B13" t="n">
-        <v>79565</v>
+        <v>97770</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1913,25 +1914,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>677079</v>
+        <v>676881</v>
       </c>
       <c r="R13" t="n">
-        <v>7085694</v>
+        <v>7085506</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2003,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118713061</v>
+        <v>118713048</v>
       </c>
       <c r="B14" t="n">
-        <v>56502</v>
+        <v>90529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2015,25 +2016,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2043,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>676939</v>
+        <v>677129</v>
       </c>
       <c r="R14" t="n">
-        <v>7085624</v>
+        <v>7085711</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2105,10 +2106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118713063</v>
+        <v>118713054</v>
       </c>
       <c r="B15" t="n">
-        <v>57181</v>
+        <v>79572</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2121,21 +2122,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100001</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2145,10 +2146,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>677034</v>
+        <v>677120</v>
       </c>
       <c r="R15" t="n">
-        <v>7085686</v>
+        <v>7085431</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2181,11 +2182,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-07-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Fågelbo på stam av rovfågel</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,10 +2208,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118713054</v>
+        <v>118713064</v>
       </c>
       <c r="B16" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2252,10 +2248,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>677120</v>
+        <v>677079</v>
       </c>
       <c r="R16" t="n">
-        <v>7085431</v>
+        <v>7085694</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,7 +2313,7 @@
         <v>118713062</v>
       </c>
       <c r="B17" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2416,10 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118713050</v>
+        <v>118713063</v>
       </c>
       <c r="B18" t="n">
-        <v>79565</v>
+        <v>57181</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2432,21 +2428,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2456,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>677135</v>
+        <v>677034</v>
       </c>
       <c r="R18" t="n">
-        <v>7085535</v>
+        <v>7085686</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,13 +2490,17 @@
           <t>2024-07-17</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Fågelbo på stam av rovfågel</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2522,7 +2522,7 @@
         <v>118515803</v>
       </c>
       <c r="B19" t="n">
-        <v>90469</v>
+        <v>90476</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 22677-2024 artfynd.xlsx
+++ b/artfynd/A 22677-2024 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118502499</v>
+        <v>118514384</v>
       </c>
       <c r="B4" t="n">
-        <v>56502</v>
+        <v>90458</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,41 +937,48 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillmyran (Lillmyran), Ång</t>
+          <t>SCA, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>677156</v>
+        <v>677104</v>
       </c>
       <c r="R4" t="n">
-        <v>7085436</v>
+        <v>7085770</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,27 +1005,18 @@
           <t>2024-07-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-17</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1037,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118505495</v>
+        <v>118505021</v>
       </c>
       <c r="B5" t="n">
-        <v>79572</v>
+        <v>90511</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,21 +1051,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1077,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>677182</v>
+        <v>677169</v>
       </c>
       <c r="R5" t="n">
-        <v>7085673</v>
+        <v>7085612</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1112,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118505021</v>
+        <v>118505495</v>
       </c>
       <c r="B6" t="n">
-        <v>90511</v>
+        <v>79572</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,21 +1163,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677169</v>
+        <v>677182</v>
       </c>
       <c r="R6" t="n">
-        <v>7085612</v>
+        <v>7085673</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1224,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118514384</v>
+        <v>118502499</v>
       </c>
       <c r="B7" t="n">
-        <v>90458</v>
+        <v>56502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,48 +1271,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>SCA, Ång</t>
+          <t>Lillmyran (Lillmyran), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>677104</v>
+        <v>677156</v>
       </c>
       <c r="R7" t="n">
-        <v>7085770</v>
+        <v>7085436</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,18 +1332,27 @@
           <t>2024-07-17</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-17</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118713066</v>
+        <v>118713062</v>
       </c>
       <c r="B9" t="n">
         <v>78491</v>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>677082</v>
+        <v>676975</v>
       </c>
       <c r="R9" t="n">
-        <v>7085390</v>
+        <v>7085592</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,11 +1559,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt på tallstam</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118713061</v>
+        <v>118713050</v>
       </c>
       <c r="B10" t="n">
-        <v>56502</v>
+        <v>79572</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,25 +1597,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1630,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>676939</v>
+        <v>677135</v>
       </c>
       <c r="R10" t="n">
-        <v>7085624</v>
+        <v>7085535</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,6 +1669,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1692,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118713050</v>
+        <v>118713048</v>
       </c>
       <c r="B11" t="n">
-        <v>79572</v>
+        <v>90529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,21 +1704,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>677135</v>
+        <v>677129</v>
       </c>
       <c r="R11" t="n">
-        <v>7085535</v>
+        <v>7085711</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,7 +1772,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1795,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118713055</v>
+        <v>118713064</v>
       </c>
       <c r="B12" t="n">
-        <v>78491</v>
+        <v>79572</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>677125</v>
+        <v>677079</v>
       </c>
       <c r="R12" t="n">
-        <v>7085428</v>
+        <v>7085694</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1871,11 +1866,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt på tallstam</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118713060</v>
+        <v>118713055</v>
       </c>
       <c r="B13" t="n">
-        <v>97770</v>
+        <v>78491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1914,25 +1904,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>676881</v>
+        <v>677125</v>
       </c>
       <c r="R13" t="n">
-        <v>7085506</v>
+        <v>7085428</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,6 +1968,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt på tallstam</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118713048</v>
+        <v>118713060</v>
       </c>
       <c r="B14" t="n">
-        <v>90529</v>
+        <v>97770</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2016,25 +2011,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2044,10 +2039,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>677129</v>
+        <v>676881</v>
       </c>
       <c r="R14" t="n">
-        <v>7085711</v>
+        <v>7085506</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2208,10 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118713064</v>
+        <v>118713063</v>
       </c>
       <c r="B16" t="n">
-        <v>79572</v>
+        <v>57181</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2224,21 +2219,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100001</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2248,10 +2243,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>677079</v>
+        <v>677034</v>
       </c>
       <c r="R16" t="n">
-        <v>7085694</v>
+        <v>7085686</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,6 +2279,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fågelbo på stam av rovfågel</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,7 +2310,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118713062</v>
+        <v>118713066</v>
       </c>
       <c r="B17" t="n">
         <v>78491</v>
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>676975</v>
+        <v>677082</v>
       </c>
       <c r="R17" t="n">
-        <v>7085592</v>
+        <v>7085390</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2386,6 +2386,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt på tallstam</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118713063</v>
+        <v>118713061</v>
       </c>
       <c r="B18" t="n">
-        <v>57181</v>
+        <v>56502</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2424,25 +2429,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100001</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2452,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>677034</v>
+        <v>676939</v>
       </c>
       <c r="R18" t="n">
-        <v>7085686</v>
+        <v>7085624</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,11 +2493,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-07-17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Fågelbo på stam av rovfågel</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 22677-2024 artfynd.xlsx
+++ b/artfynd/A 22677-2024 artfynd.xlsx
@@ -2104,7 +2104,7 @@
         <v>118713063</v>
       </c>
       <c r="B15" t="n">
-        <v>57183</v>
+        <v>57201</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2135,6 +2135,10 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>A 22677-2024, Ång</t>

--- a/artfynd/A 22677-2024 artfynd.xlsx
+++ b/artfynd/A 22677-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2627,112 +2627,6 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>118883686</v>
-      </c>
-      <c r="B20" t="n">
-        <v>57183</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>100001</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Duvhök</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Accipiter gentilis</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>SCA, Ång</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>676942</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7085721</v>
-      </c>
-      <c r="S20" t="n">
-        <v>50</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2024-07-17</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2024-07-17</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22677-2024 artfynd.xlsx
+++ b/artfynd/A 22677-2024 artfynd.xlsx
@@ -2104,7 +2104,7 @@
         <v>118713063</v>
       </c>
       <c r="B15" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 22677-2024 artfynd.xlsx
+++ b/artfynd/A 22677-2024 artfynd.xlsx
@@ -2104,7 +2104,7 @@
         <v>118713063</v>
       </c>
       <c r="B15" t="n">
-        <v>57265</v>
+        <v>57270</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 22677-2024 artfynd.xlsx
+++ b/artfynd/A 22677-2024 artfynd.xlsx
@@ -2119,11 +2119,6 @@
       <c r="E15" t="n">
         <v>100001</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Duvhök</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Astur gentilis</t>

--- a/artfynd/A 22677-2024 artfynd.xlsx
+++ b/artfynd/A 22677-2024 artfynd.xlsx
@@ -2104,7 +2104,7 @@
         <v>118713063</v>
       </c>
       <c r="B15" t="n">
-        <v>57270</v>
+        <v>57274</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2118,6 +2118,11 @@
       </c>
       <c r="E15" t="n">
         <v>100001</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>

--- a/artfynd/A 22677-2024 artfynd.xlsx
+++ b/artfynd/A 22677-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7215156</v>
+        <v>118504168</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grönåker, Ång</t>
+          <t>Lillmyran, Lillmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>677091.2632008337</v>
+        <v>677154</v>
       </c>
       <c r="R2" t="n">
-        <v>7085703.932355304</v>
+        <v>7085619</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-06-21</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-06-21</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,44 +766,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter # sälg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulf Hallin</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulf Hallin, Niina Sallmén</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7215157</v>
+        <v>118514384</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,37 +793,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grönåker, Ång</t>
+          <t>SCA, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>677066.5440153818</v>
+        <v>677104</v>
       </c>
       <c r="R3" t="n">
-        <v>7085608.834208832</v>
+        <v>7085770</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,22 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-06-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-06-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,46 +868,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>1 substratenheter # granlåga</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulf Hallin</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulf Hallin, Niina Sallmén</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118514384</v>
+        <v>7215157</v>
       </c>
       <c r="B4" t="n">
-        <v>90460</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,44 +898,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>SCA, Ång</t>
+          <t>Grönåker, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>677104</v>
+        <v>677067</v>
       </c>
       <c r="R4" t="n">
-        <v>7085770</v>
+        <v>7085609</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,12 +952,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2013-06-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2013-06-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,19 +966,31 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1 substratenheter # granlåga</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Ulf Hallin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Ulf Hallin, Niina Sallmén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1038,12 +1000,7 @@
         <v>118505021</v>
       </c>
       <c r="B5" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1028,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillmyran (Lillmyran), Ång</t>
+          <t>Lillmyran, Lillmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1147,53 +1104,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118505495</v>
+        <v>118515803</v>
       </c>
       <c r="B6" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillmyran (Lillmyran), Ång</t>
+          <t>SCA, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677182</v>
+        <v>677056</v>
       </c>
       <c r="R6" t="n">
-        <v>7085673</v>
+        <v>7085748</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,27 +1175,18 @@
           <t>2024-07-17</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-17</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1259,53 +1205,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118502499</v>
+        <v>118713055</v>
       </c>
       <c r="B7" t="n">
-        <v>56504</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillmyran (Lillmyran), Ång</t>
+          <t>A 22677-2024, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>677156</v>
+        <v>677125</v>
       </c>
       <c r="R7" t="n">
-        <v>7085436</v>
+        <v>7085428</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1332,19 +1273,14 @@
           <t>2024-07-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-17</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:04</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt på tallstam</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,27 +1295,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118504168</v>
+        <v>118713062</v>
       </c>
       <c r="B8" t="n">
-        <v>90703</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,37 +1318,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillmyran (Lillmyran), Ång</t>
+          <t>A 22677-2024, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>677154</v>
+        <v>676975</v>
       </c>
       <c r="R8" t="n">
-        <v>7085619</v>
+        <v>7085592</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,19 +1375,9 @@
           <t>2024-07-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,12 +1392,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1486,16 +1407,11 @@
         <v>118713066</v>
       </c>
       <c r="B9" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1590,50 +1506,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118713061</v>
+        <v>7215156</v>
       </c>
       <c r="B10" t="n">
-        <v>56504</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 22677-2024, Ång</t>
+          <t>Grönåker, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>676939</v>
+        <v>677091</v>
       </c>
       <c r="R10" t="n">
-        <v>7085624</v>
+        <v>7085704</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1660,12 +1571,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2013-06-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2013-06-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,31 +1587,39 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>1 substratenheter # sälg</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Ulf Hallin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Ulf Hallin, Niina Sallmén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118713050</v>
+        <v>118502615</v>
       </c>
       <c r="B11" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,17 +1647,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 22677-2024, Ång</t>
+          <t>Lillmyran, Lillmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>677135</v>
+        <v>677169</v>
       </c>
       <c r="R11" t="n">
-        <v>7085535</v>
+        <v>7085434</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1765,45 +1684,49 @@
           <t>2024-07-17</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-17</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118713064</v>
+        <v>118505495</v>
       </c>
       <c r="B12" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,17 +1754,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 22677-2024, Ång</t>
+          <t>Lillmyran, Lillmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>677079</v>
+        <v>677182</v>
       </c>
       <c r="R12" t="n">
-        <v>7085694</v>
+        <v>7085673</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1868,9 +1791,19 @@
           <t>2024-07-17</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1885,27 +1818,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118713054</v>
+        <v>118713050</v>
       </c>
       <c r="B13" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,10 +1865,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>677120</v>
+        <v>677135</v>
       </c>
       <c r="R13" t="n">
-        <v>7085431</v>
+        <v>7085535</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1981,6 +1909,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1999,15 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118713048</v>
+        <v>118713052</v>
       </c>
       <c r="B14" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,21 +1939,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2039,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>677129</v>
+        <v>677150</v>
       </c>
       <c r="R14" t="n">
-        <v>7085711</v>
+        <v>7085504</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2083,6 +2007,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2101,15 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118713063</v>
+        <v>118713054</v>
       </c>
       <c r="B15" t="n">
-        <v>57274</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,38 +2037,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100001</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>A 22677-2024, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>677034</v>
+        <v>677120</v>
       </c>
       <c r="R15" t="n">
-        <v>7085686</v>
+        <v>7085431</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2181,11 +2097,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-07-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Fågelbo på stam av rovfågel</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,15 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118713062</v>
+        <v>118713064</v>
       </c>
       <c r="B16" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2252,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>676975</v>
+        <v>677079</v>
       </c>
       <c r="R16" t="n">
-        <v>7085592</v>
+        <v>7085694</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2314,15 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118713060</v>
+        <v>16944979</v>
       </c>
       <c r="B17" t="n">
-        <v>97775</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,37 +2231,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 22677-2024, Ång</t>
+          <t>Lillsjölidtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>676881</v>
+        <v>677155</v>
       </c>
       <c r="R17" t="n">
-        <v>7085506</v>
+        <v>7085513</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2384,12 +2285,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2400,31 +2301,41 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118713055</v>
+        <v>118713063</v>
       </c>
       <c r="B18" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,34 +2343,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>A 22677-2024, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>677125</v>
+        <v>677034</v>
       </c>
       <c r="R18" t="n">
-        <v>7085428</v>
+        <v>7085686</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2496,7 +2411,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt på tallstam</t>
+          <t>Fågelbo på stam av rovfågel</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2523,15 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118515803</v>
+        <v>118502499</v>
       </c>
       <c r="B19" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,40 +2449,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>SCA, Ång</t>
+          <t>Lillmyran, Lillmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>677056</v>
+        <v>677156</v>
       </c>
       <c r="R19" t="n">
-        <v>7085748</v>
+        <v>7085436</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2599,18 +2506,27 @@
           <t>2024-07-17</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-07-17</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2626,6 +2542,510 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>118713061</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 22677-2024, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>676939</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7085624</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>118713053</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 22677-2024, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>677148</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7085489</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>118713060</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A 22677-2024, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>676881</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7085506</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>118517303</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SCA, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>677061</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7085787</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>118503007</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lillmyran, Lillmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>677147</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7085488</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22677-2024 artfynd.xlsx
+++ b/artfynd/A 22677-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504168</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118514384</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7215157</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505021</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118515803</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118713055</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1401,6 +1436,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118713062</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1503,6 +1543,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118713066</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1613,6 +1658,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7215156</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1720,6 +1770,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118502615</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1827,6 +1882,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505495</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1925,6 +1985,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118713050</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2023,6 +2088,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118713052</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2120,6 +2190,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118713054</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2217,6 +2292,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118713064</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2329,6 +2409,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16944979</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2435,6 +2520,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118713063</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2542,6 +2632,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118502499</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2639,6 +2734,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118713061</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2736,6 +2836,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118713053</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2833,6 +2938,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118713060</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2939,6 +3049,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118517303</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3046,8 +3161,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118503007</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>